--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1022"/>
+  <dimension ref="A1:Z1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44267</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44342</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44343</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44378</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44406</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44411</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44427</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44463</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44494</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44616</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44786</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44820</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44858</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44978</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45182</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45195</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45224</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45225</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43335</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43340</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43357</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43369</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43377</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43404</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43413</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43420</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43421</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43422</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43427</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43440</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43447</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43455</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>43465</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>43469</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>43471</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>43472</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>43473</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43474</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43476</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43478</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43482</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43485</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>43486</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43488</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43493</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43500</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43507</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43509</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43517</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43529</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43531</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43538</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43542</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43543</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43544</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43549</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43552</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>43556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>43557</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>43558</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>43566</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>43567</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43579</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43595</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>43606</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>43607</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43613</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>43630</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43641</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43647</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43648</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>43649</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>43654</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>43655</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>43665</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>43669</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>43676</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>43693</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>43696</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>43699</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>43703</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>43706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>43707</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>43709</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>43713</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43718</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43721</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43732</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43734</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43737</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43742</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43745</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43749</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>43758</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>43759</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43761</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>43767</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>43769</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>43774</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>43775</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>43780</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>43783</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>43797</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>43801</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>43805</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>43809</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>43810</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>43815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>43818</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>43835</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>43837</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>43840</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>43843</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>43846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>43851</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>43853</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>43858</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>43859</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>43860</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>43861</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>43864</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>43873</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>43875</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>43878</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>43880</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>43881</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>43882</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>43883</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>43886</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>43899</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>43901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>43907</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>43920</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>43927</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>43930</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>43937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>43938</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>43945</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>43951</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>43955</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>43962</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>43965</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>43970</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>43971</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>43976</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>43979</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>43993</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44002</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44007</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44011</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44012</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44014</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44028</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44069</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44071</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44081</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44083</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44098</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44099</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44102</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44103</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44104</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44106</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44109</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44127</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44130</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44133</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44139</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44144</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44145</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44153</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44154</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44158</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44160</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44165</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44166</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44168</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44169</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44181</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51656,7 +51656,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60777,14 +60777,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 5056-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -60834,14 +60834,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 5054-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -60898,7 +60898,7 @@
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60948,14 +60948,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 5056-2024</t>
+          <t>A 5054-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61005,14 +61005,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 5111-2024</t>
+          <t>A 5145-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -61062,14 +61062,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 5145-2024</t>
+          <t>A 5111-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -61119,14 +61119,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 5563-2024</t>
+          <t>A 5553-2024</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -61176,14 +61176,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 5616-2024</t>
+          <t>A 5563-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -61230,62 +61230,233 @@
       </c>
       <c r="R1021" s="2" t="inlineStr"/>
     </row>
-    <row r="1022">
+    <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 5553-2024</t>
+          <t>A 5616-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1022" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1022" s="2" t="inlineStr"/>
+    </row>
+    <row r="1023" ht="15" customHeight="1">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>A 6117-2024</t>
+        </is>
+      </c>
+      <c r="B1023" s="1" t="n">
         <v>45337</v>
       </c>
-      <c r="D1022" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="E1022" t="inlineStr">
-        <is>
-          <t>OSKARSHAMN</t>
-        </is>
-      </c>
-      <c r="G1022" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1022" s="2" t="inlineStr"/>
+      <c r="C1023" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1023" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1023" s="2" t="inlineStr"/>
+    </row>
+    <row r="1024" ht="15" customHeight="1">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>A 6123-2024</t>
+        </is>
+      </c>
+      <c r="B1024" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C1024" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1024" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1024" s="2" t="inlineStr"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>A 6136-2024</t>
+        </is>
+      </c>
+      <c r="B1025" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C1025" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1025" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1025" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44267</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44342</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44343</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44378</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44406</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44411</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44427</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44463</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44494</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44616</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44786</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44820</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44858</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44978</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45182</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45195</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45224</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45225</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43335</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43340</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43357</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43369</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43377</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43404</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43413</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43420</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43421</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43422</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43427</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43440</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43447</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43455</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>43465</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>43469</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>43471</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>43472</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>43473</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43474</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43476</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43478</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43482</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43485</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>43486</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43488</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43493</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43500</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43507</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43509</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43517</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43529</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43531</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43538</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43542</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43543</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43544</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43549</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43552</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>43556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>43557</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>43558</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>43566</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>43567</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43579</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43595</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>43606</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>43607</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43613</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>43630</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43641</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43647</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43648</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>43649</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>43654</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>43655</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>43665</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>43669</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>43676</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>43693</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>43696</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>43699</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>43703</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>43706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>43707</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>43709</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>43713</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43718</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43721</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43732</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43734</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43737</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43742</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43745</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43749</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>43758</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>43759</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43761</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>43767</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>43769</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>43774</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>43775</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>43780</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>43783</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>43797</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>43801</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>43805</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>43809</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>43810</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>43815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>43818</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>43835</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>43837</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>43840</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>43843</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>43846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>43851</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>43853</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>43858</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>43859</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>43860</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>43861</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>43864</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>43873</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>43875</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>43878</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>43880</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>43881</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>43882</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>43883</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>43886</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>43899</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>43901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>43907</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>43920</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>43927</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>43930</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>43937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>43938</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>43945</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>43951</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>43955</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>43962</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>43965</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>43970</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>43971</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>43976</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>43979</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>43993</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44002</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44007</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44011</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44012</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44014</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44028</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44069</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44071</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44081</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44083</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44098</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44099</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44102</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44103</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44104</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44106</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44109</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44127</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44130</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44133</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44139</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44144</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44145</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44153</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44154</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44158</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44160</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44165</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44166</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44168</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44169</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44181</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51656,7 +51656,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60777,14 +60777,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 5056-2024</t>
+          <t>A 5046-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -60834,14 +60834,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 5056-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -60891,14 +60891,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 5046-2024</t>
+          <t>A 5054-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -60948,14 +60948,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 5054-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61005,14 +61005,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 5145-2024</t>
+          <t>A 5111-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -61062,14 +61062,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 5111-2024</t>
+          <t>A 5145-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -61126,7 +61126,7 @@
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61176,14 +61176,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 5563-2024</t>
+          <t>A 5616-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -61233,14 +61233,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 5616-2024</t>
+          <t>A 5563-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -61297,7 +61297,7 @@
         <v>45337</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61347,14 +61347,14 @@
     <row r="1024" ht="15" customHeight="1">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>A 6123-2024</t>
+          <t>A 6136-2024</t>
         </is>
       </c>
       <c r="B1024" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -61404,14 +61404,14 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 6136-2024</t>
+          <t>A 6123-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1025"/>
+  <dimension ref="A1:Z1027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44267</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44342</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44343</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44378</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44406</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44411</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44427</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44463</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44494</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44616</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44786</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44820</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44858</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44978</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45182</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45195</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45224</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45225</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43335</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43340</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43357</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43369</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43377</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43404</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43413</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43420</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43421</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43422</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43427</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43440</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43447</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43455</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>43465</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>43469</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>43471</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>43472</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>43473</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43474</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43476</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43478</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43482</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43485</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>43486</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43488</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43493</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43500</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43507</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43509</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43517</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43529</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43531</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43538</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43542</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43543</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43544</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43549</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43552</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>43556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>43557</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>43558</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>43566</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>43567</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43579</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43595</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>43606</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>43607</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43613</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>43630</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43641</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43647</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43648</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>43649</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>43654</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>43655</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>43665</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>43669</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>43676</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>43693</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>43696</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>43699</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>43703</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>43706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>43707</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>43709</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>43713</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43718</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43721</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43732</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43734</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43737</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43742</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43745</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43749</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>43758</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>43759</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43761</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>43767</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>43769</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>43774</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>43775</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>43780</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>43783</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>43797</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>43801</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>43805</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>43809</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>43810</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>43815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>43818</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>43835</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>43837</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>43840</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>43843</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>43846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>43851</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>43853</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>43858</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>43859</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>43860</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>43861</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>43864</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>43873</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>43875</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>43878</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>43880</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>43881</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>43882</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>43883</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>43886</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>43899</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>43901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>43907</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>43920</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>43927</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>43930</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>43937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>43938</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>43945</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>43951</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>43955</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>43962</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>43965</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>43970</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>43971</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>43976</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>43979</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>43993</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44002</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44007</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44011</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44012</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44014</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44028</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44069</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44071</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44081</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44083</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44098</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44099</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44102</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44103</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44104</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44106</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44109</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44127</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44130</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44133</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44139</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44144</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44145</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44153</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44154</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44158</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44160</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44165</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44166</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44168</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44169</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44181</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51656,7 +51656,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60435,14 +60435,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4097-2024</t>
+          <t>A 4074-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60492,14 +60492,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 4074-2024</t>
+          <t>A 4097-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60512,7 +60512,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60556,7 +60556,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60663,14 +60663,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 4880-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60683,7 +60683,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>2.7</v>
+        <v>7.1</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60720,14 +60720,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 4962-2024</t>
+          <t>A 4880-2024</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60777,14 +60777,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 5046-2024</t>
+          <t>A 4962-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -60841,7 +60841,7 @@
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60891,14 +60891,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 5054-2024</t>
+          <t>A 5046-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -60948,14 +60948,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 5054-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61012,7 +61012,7 @@
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61126,7 +61126,7 @@
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61240,7 +61240,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45337</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>45337</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
       </c>
       <c r="R1024" s="2" t="inlineStr"/>
     </row>
-    <row r="1025">
+    <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
           <t>A 6123-2024</t>
@@ -61411,7 +61411,7 @@
         <v>45337</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61457,6 +61457,120 @@
         <v>0</v>
       </c>
       <c r="R1025" s="2" t="inlineStr"/>
+    </row>
+    <row r="1026" ht="15" customHeight="1">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>A 6670-2024</t>
+        </is>
+      </c>
+      <c r="B1026" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C1026" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1026" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1026" s="2" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>A 6671-2024</t>
+        </is>
+      </c>
+      <c r="B1027" s="1" t="n">
+        <v>45341</v>
+      </c>
+      <c r="C1027" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1027" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1027" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44267</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44342</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44343</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44378</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44406</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44411</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44427</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44463</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44494</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44616</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44786</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44820</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44858</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44978</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45182</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45195</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45224</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45225</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43335</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43340</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43357</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43369</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43377</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43404</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43413</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43420</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43421</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43422</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43427</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43440</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43447</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43455</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>43465</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>43469</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>43471</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>43472</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>43473</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43474</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43476</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43478</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43482</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43485</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>43486</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43488</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43493</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43500</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43507</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43509</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43517</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43529</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43531</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43538</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43542</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43543</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43544</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43549</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43552</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>43556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>43557</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>43558</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>43566</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>43567</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43579</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43595</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>43606</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>43607</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43613</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>43630</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43641</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43647</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43648</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>43649</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>43654</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>43655</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>43665</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>43669</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>43676</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>43693</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>43696</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>43699</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>43703</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>43706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>43707</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>43709</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>43713</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43718</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43721</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43732</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43734</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43737</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43742</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43745</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43749</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>43758</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>43759</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43761</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>43767</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>43769</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>43774</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>43775</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>43780</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>43783</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>43797</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>43801</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>43805</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>43809</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>43810</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>43815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>43818</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>43835</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>43837</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>43840</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>43843</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>43846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>43851</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>43853</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>43858</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>43859</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>43860</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>43861</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>43864</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>43873</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>43875</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>43878</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>43880</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>43881</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>43882</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>43883</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>43886</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>43899</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>43901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>43907</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>43920</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>43927</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>43930</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>43937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>43938</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>43945</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>43951</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>43955</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>43962</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>43965</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>43970</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>43971</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>43976</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>43979</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>43993</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44002</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44007</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44011</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44012</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44014</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44028</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44069</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44071</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44081</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44083</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44098</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44099</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44102</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44103</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44104</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44106</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44109</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44127</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44130</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44133</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44139</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44144</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44145</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44153</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44154</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44158</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44160</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44165</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44166</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44168</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44169</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44181</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51656,7 +51656,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60435,14 +60435,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4074-2024</t>
+          <t>A 4097-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60492,14 +60492,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 4097-2024</t>
+          <t>A 4074-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60512,7 +60512,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60556,7 +60556,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60663,14 +60663,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 5046-2024</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60683,7 +60683,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60720,14 +60720,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 4880-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>2.7</v>
+        <v>7.1</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60777,14 +60777,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 4962-2024</t>
+          <t>A 5054-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -60834,14 +60834,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 5056-2024</t>
+          <t>A 4880-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -60891,14 +60891,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 5046-2024</t>
+          <t>A 4962-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -60948,14 +60948,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 5054-2024</t>
+          <t>A 5056-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61012,7 +61012,7 @@
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61119,14 +61119,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 5553-2024</t>
+          <t>A 5563-2024</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -61176,14 +61176,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 5616-2024</t>
+          <t>A 5553-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -61233,14 +61233,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 5563-2024</t>
+          <t>A 5616-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -61297,7 +61297,7 @@
         <v>45337</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>45337</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>45337</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61461,14 +61461,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 6670-2024</t>
+          <t>A 6671-2024</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -61518,14 +61518,14 @@
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 6671-2024</t>
+          <t>A 6670-2024</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1027"/>
+  <dimension ref="A1:Z1030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44267</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44342</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44343</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44378</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44406</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44411</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44427</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44463</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44494</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44616</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44786</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44820</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44858</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44978</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45182</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45195</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45224</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45225</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43335</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43340</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43357</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43369</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43377</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43404</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43413</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43420</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43421</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43422</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43427</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43440</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43447</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43455</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>43465</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>43469</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>43471</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>43472</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>43473</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43474</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43476</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43478</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43482</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43485</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>43486</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43488</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43493</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43500</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43507</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43509</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43517</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43529</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43531</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43538</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43542</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43543</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43544</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43549</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43552</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>43556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>43557</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>43558</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>43566</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>43567</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43579</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43595</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>43606</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>43607</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43613</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>43630</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43641</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43647</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43648</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>43649</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>43654</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>43655</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>43665</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>43669</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>43676</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>43693</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>43696</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>43699</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>43703</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>43706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>43707</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>43709</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>43713</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43718</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43721</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43732</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43734</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43737</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43742</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43745</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43749</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>43758</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>43759</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43761</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>43767</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>43769</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>43774</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>43775</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>43780</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>43783</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>43797</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>43801</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>43805</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>43809</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>43810</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>43815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>43818</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>43835</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>43837</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>43840</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>43843</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>43846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>43851</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>43853</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>43858</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>43859</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>43860</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>43861</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>43864</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>43873</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>43875</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>43878</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>43880</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>43881</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>43882</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>43883</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>43886</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>43899</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>43901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>43907</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>43920</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>43927</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>43930</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>43937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>43938</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>43945</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>43951</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>43955</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>43962</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>43965</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>43970</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>43971</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>43976</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>43979</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>43993</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44002</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44007</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44011</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44012</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44014</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44028</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44069</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44071</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44081</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44083</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44098</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44099</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44102</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44103</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44104</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44106</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44109</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44127</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44130</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44133</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44139</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44144</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44145</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44153</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44154</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44158</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44160</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44165</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44166</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44168</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44169</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44181</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51656,7 +51656,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60088,14 +60088,14 @@
     <row r="1002" ht="15" customHeight="1">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>A 2778-2024</t>
+          <t>A 2782-2024</t>
         </is>
       </c>
       <c r="B1002" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60108,7 +60108,7 @@
         </is>
       </c>
       <c r="G1002" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="H1002" t="n">
         <v>0</v>
@@ -60145,14 +60145,14 @@
     <row r="1003" ht="15" customHeight="1">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>A 2782-2024</t>
+          <t>A 2778-2024</t>
         </is>
       </c>
       <c r="B1003" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60165,7 +60165,7 @@
         </is>
       </c>
       <c r="G1003" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="H1003" t="n">
         <v>0</v>
@@ -60209,7 +60209,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60435,14 +60435,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4097-2024</t>
+          <t>A 4074-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60492,14 +60492,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 4074-2024</t>
+          <t>A 4097-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60512,7 +60512,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60556,7 +60556,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60720,14 +60720,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 4880-2024</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60784,7 +60784,7 @@
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60834,14 +60834,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 4880-2024</t>
+          <t>A 4962-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -60891,14 +60891,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 4962-2024</t>
+          <t>A 5056-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -60948,14 +60948,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 5056-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61012,7 +61012,7 @@
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61119,14 +61119,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 5563-2024</t>
+          <t>A 5553-2024</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -61176,14 +61176,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 5553-2024</t>
+          <t>A 5616-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -61233,14 +61233,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 5616-2024</t>
+          <t>A 5563-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -61290,14 +61290,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 6117-2024</t>
+          <t>A 6123-2024</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -61354,7 +61354,7 @@
         <v>45337</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61404,14 +61404,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 6123-2024</t>
+          <t>A 6117-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -61468,7 +61468,7 @@
         <v>45341</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61515,7 +61515,7 @@
       </c>
       <c r="R1026" s="2" t="inlineStr"/>
     </row>
-    <row r="1027">
+    <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
           <t>A 6670-2024</t>
@@ -61525,7 +61525,7 @@
         <v>45341</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61571,6 +61571,177 @@
         <v>0</v>
       </c>
       <c r="R1027" s="2" t="inlineStr"/>
+    </row>
+    <row r="1028" ht="15" customHeight="1">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>A 7141-2024</t>
+        </is>
+      </c>
+      <c r="B1028" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C1028" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1028" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1028" s="2" t="inlineStr"/>
+    </row>
+    <row r="1029" ht="15" customHeight="1">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>A 7148-2024</t>
+        </is>
+      </c>
+      <c r="B1029" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C1029" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1029" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1029" s="2" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>A 7250-2024</t>
+        </is>
+      </c>
+      <c r="B1030" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C1030" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1030" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1030" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44267</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44342</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44343</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44378</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44406</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44411</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44427</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44463</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44494</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44616</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44786</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44820</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44858</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44978</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45182</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45195</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45224</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45225</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43335</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43340</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43357</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43369</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43377</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43404</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43413</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43420</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43421</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43422</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43427</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43440</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43447</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43455</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>43465</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>43469</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>43471</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>43472</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>43473</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43474</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43476</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43478</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43482</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43485</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>43486</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43488</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43493</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43500</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43507</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43509</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43517</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43529</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43531</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43538</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43542</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43543</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43544</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43549</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43552</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>43556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>43557</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>43558</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>43566</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>43567</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43579</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43595</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>43606</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>43607</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43613</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>43630</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43641</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43647</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43648</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>43649</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>43654</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>43655</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>43665</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>43669</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>43676</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>43693</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>43696</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>43699</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>43703</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>43706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>43707</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>43709</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>43713</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43718</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43721</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43732</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43734</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43737</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43742</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43745</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43749</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>43758</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>43759</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43761</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>43767</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>43769</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>43774</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>43775</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>43780</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>43783</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>43797</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>43801</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>43805</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>43809</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>43810</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>43815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>43818</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>43835</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>43837</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>43840</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>43843</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>43846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>43851</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>43853</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>43858</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>43859</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>43860</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>43861</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>43864</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>43873</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>43875</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>43878</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>43880</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>43881</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>43882</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>43883</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>43886</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>43899</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>43901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>43907</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>43920</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>43927</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>43930</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>43937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>43938</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>43945</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>43951</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>43955</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>43962</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>43965</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>43970</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>43971</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>43976</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>43979</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>43993</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44002</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44007</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44011</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44012</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44014</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44028</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44069</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44071</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44081</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44083</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44098</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44099</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44102</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44103</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44104</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44106</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44109</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44127</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44130</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44133</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44139</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44144</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44145</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44153</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44154</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44158</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44160</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44165</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44166</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44168</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44169</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44181</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51656,7 +51656,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60663,14 +60663,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 5046-2024</t>
+          <t>A 4880-2024</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60683,7 +60683,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60720,14 +60720,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 4880-2024</t>
+          <t>A 4962-2024</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60777,14 +60777,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 5054-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -60834,14 +60834,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 4962-2024</t>
+          <t>A 5056-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -60891,14 +60891,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 5056-2024</t>
+          <t>A 5046-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -60948,14 +60948,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 5054-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61005,14 +61005,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 5111-2024</t>
+          <t>A 5145-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -61062,14 +61062,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 5145-2024</t>
+          <t>A 5111-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -61119,14 +61119,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 5553-2024</t>
+          <t>A 5563-2024</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -61176,14 +61176,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 5616-2024</t>
+          <t>A 5553-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -61233,14 +61233,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 5563-2024</t>
+          <t>A 5616-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -61290,14 +61290,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 6123-2024</t>
+          <t>A 6117-2024</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -61347,14 +61347,14 @@
     <row r="1024" ht="15" customHeight="1">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>A 6136-2024</t>
+          <t>A 6123-2024</t>
         </is>
       </c>
       <c r="B1024" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -61404,14 +61404,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 6117-2024</t>
+          <t>A 6136-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -61461,14 +61461,14 @@
     <row r="1026" ht="15" customHeight="1">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>A 6671-2024</t>
+          <t>A 6670-2024</t>
         </is>
       </c>
       <c r="B1026" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="H1026" t="n">
         <v>0</v>
@@ -61518,14 +61518,14 @@
     <row r="1027" ht="15" customHeight="1">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>A 6670-2024</t>
+          <t>A 6671-2024</t>
         </is>
       </c>
       <c r="B1027" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         </is>
       </c>
       <c r="G1027" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="H1027" t="n">
         <v>0</v>
@@ -61575,14 +61575,14 @@
     <row r="1028" ht="15" customHeight="1">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 7141-2024</t>
+          <t>A 7250-2024</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -61632,14 +61632,14 @@
     <row r="1029" ht="15" customHeight="1">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>A 7148-2024</t>
+          <t>A 7141-2024</t>
         </is>
       </c>
       <c r="B1029" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61652,7 +61652,7 @@
         </is>
       </c>
       <c r="G1029" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -61689,14 +61689,14 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>A 7250-2024</t>
+          <t>A 7148-2024</t>
         </is>
       </c>
       <c r="B1030" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61709,7 +61709,7 @@
         </is>
       </c>
       <c r="G1030" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="H1030" t="n">
         <v>0</v>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44267</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44342</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44343</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44356</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44378</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44406</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44411</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44427</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44463</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44494</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44616</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>44778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44786</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44820</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>44858</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>44978</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45098</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45182</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45195</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45224</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45225</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>43335</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>43339</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>43340</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>43357</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>43369</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>43377</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>43402</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>43403</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43404</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43413</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43420</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>43421</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>43422</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>43424</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>43427</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>43430</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>43432</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43440</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43447</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>43452</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43453</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>43454</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>43455</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>43465</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>43469</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>43471</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>43472</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>43473</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>43474</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>43475</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>43476</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43478</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>43479</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>43482</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>43485</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>43486</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>43488</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>43493</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>43500</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>43507</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>43509</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>43516</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>43517</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9874,7 +9874,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>43529</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>43531</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43538</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43542</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>43543</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43544</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43549</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>43552</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>43556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>43557</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>43558</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>43566</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>43567</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>43579</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>43587</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>43595</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>43606</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>43607</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>43608</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>43613</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>43619</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>43630</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>43633</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>43640</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>43641</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>43644</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>43647</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>43648</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>43649</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>43654</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>43655</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>43657</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>43665</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>43669</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43675</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>43676</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>43693</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>43696</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>43698</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>43699</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>43703</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>43706</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>43707</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>43709</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>43713</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>43718</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>43719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43721</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>43732</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>43734</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>43737</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>43742</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>43745</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>43749</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>43758</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>43759</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>43761</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>43767</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>43769</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>43774</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>43775</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>43780</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>43783</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>43787</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>43797</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>43801</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>43805</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>43809</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>43810</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>43815</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>43818</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>43835</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>43837</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>43840</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>43843</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>43846</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>43851</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>43853</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>43858</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>43859</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>43860</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>43861</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>43864</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>43873</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>43875</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>43878</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>43880</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>43881</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>43882</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>43883</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>43886</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>43899</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>43901</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>43907</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>43920</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>43927</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>43930</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>43937</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>43938</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>43945</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>43951</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19679,7 +19679,7 @@
         <v>43955</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>43962</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>43965</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>43970</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>43971</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>43976</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>43979</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>43993</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44002</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44007</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44011</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44012</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44014</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>44028</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>44053</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44069</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44071</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44081</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44083</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>44098</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44099</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44102</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44103</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44104</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44106</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44109</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>44118</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44127</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44130</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>44133</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44139</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44144</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>44145</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>44153</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44154</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44158</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44160</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44162</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44165</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44166</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44168</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>44169</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44181</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32763,7 +32763,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33395,7 +33395,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35048,7 +35048,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35105,7 +35105,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37519,7 +37519,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37747,7 +37747,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37804,7 +37804,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38384,7 +38384,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38954,7 +38954,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43683,7 +43683,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43797,7 +43797,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44025,7 +44025,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44139,7 +44139,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44253,7 +44253,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44424,7 +44424,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45569,7 +45569,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45683,7 +45683,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45854,7 +45854,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46709,7 +46709,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48724,7 +48724,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49755,7 +49755,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49983,7 +49983,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50097,7 +50097,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50838,7 +50838,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50952,7 +50952,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51371,7 +51371,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51656,7 +51656,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51770,7 +51770,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52112,7 +52112,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52454,7 +52454,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52568,7 +52568,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52801,7 +52801,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52915,7 +52915,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53029,7 +53029,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53086,7 +53086,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53143,7 +53143,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53314,7 +53314,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53884,7 +53884,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54055,7 +54055,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54112,7 +54112,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54283,7 +54283,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54454,7 +54454,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54568,7 +54568,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54682,7 +54682,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54910,7 +54910,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55081,7 +55081,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55138,7 +55138,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55195,7 +55195,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56278,7 +56278,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56449,7 +56449,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56563,7 +56563,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57019,7 +57019,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57247,7 +57247,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57304,7 +57304,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57418,7 +57418,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57646,7 +57646,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58444,7 +58444,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58568,7 +58568,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58692,7 +58692,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58754,7 +58754,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59582,7 +59582,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60442,7 +60442,7 @@
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60777,14 +60777,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 5056-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -60834,14 +60834,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 5056-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -60891,14 +60891,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 5046-2024</t>
+          <t>A 5054-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -60948,14 +60948,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 5054-2024</t>
+          <t>A 5046-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61005,14 +61005,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 5145-2024</t>
+          <t>A 5111-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -61062,14 +61062,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 5111-2024</t>
+          <t>A 5145-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -61126,7 +61126,7 @@
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61240,7 +61240,7 @@
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45337</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>45337</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>45337</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>45341</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61525,7 +61525,7 @@
         <v>45341</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61575,14 +61575,14 @@
     <row r="1028" ht="15" customHeight="1">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>A 7250-2024</t>
+          <t>A 7141-2024</t>
         </is>
       </c>
       <c r="B1028" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         </is>
       </c>
       <c r="G1028" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -61632,14 +61632,14 @@
     <row r="1029" ht="15" customHeight="1">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>A 7141-2024</t>
+          <t>A 7250-2024</t>
         </is>
       </c>
       <c r="B1029" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61652,7 +61652,7 @@
         </is>
       </c>
       <c r="G1029" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -61696,7 +61696,7 @@
         <v>45344</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1030"/>
+  <dimension ref="A1:Z1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44181</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44267</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44342</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44343</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44356</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44378</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44406</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44411</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44427</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44463</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44494</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44616</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>44778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44786</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44820</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44858</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44978</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45098</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45182</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45195</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45224</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>45225</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>43335</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>43340</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>43357</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>43377</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>43402</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43403</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43404</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>43413</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>43420</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>43421</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>43422</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>43427</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>43430</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>43432</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>43447</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>43452</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>43455</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>43465</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>43469</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>43471</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>43472</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>43473</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>43474</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>43475</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>43476</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>43478</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>43479</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>43482</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>43485</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>43486</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>43488</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>43493</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>43500</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>43507</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>43509</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>43514</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>43516</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>43517</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43529</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43531</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43536</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43538</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43542</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43543</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>43544</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>43549</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43552</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>43558</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>43566</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>43567</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>43579</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>43595</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>43607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43608</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>43613</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43630</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43633</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43640</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43641</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43644</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43648</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43649</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43654</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43655</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43657</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43665</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>43669</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>43675</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>43676</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>43693</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>43696</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>43698</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>43699</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>43703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>43706</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>43707</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43709</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>43713</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>43719</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>43721</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>43726</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>43732</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>43734</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>43737</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>43742</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>43745</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>43749</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>43758</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>43759</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>43767</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>43769</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>43774</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>43775</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>43780</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>43783</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>43787</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>43797</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>43801</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>43805</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>43809</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>43810</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>43815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>43840</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>43843</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>43846</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>43851</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>43853</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>43858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>43859</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>43860</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>43861</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>43864</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>43873</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>43875</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>43878</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>43880</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>43881</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>43882</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>43886</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>43899</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>43901</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>43907</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>43920</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>43921</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>43927</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>43930</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>43937</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>43938</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>43945</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>43951</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>43955</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>43962</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>43965</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>43970</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>43971</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>43976</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>43979</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>43993</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44002</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44011</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44012</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44014</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44028</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44053</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>44069</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>44071</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>44081</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44083</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44098</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44099</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44102</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44103</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44104</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44106</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44118</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44127</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44130</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44133</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44139</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44144</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44145</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44153</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44154</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>44158</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44160</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44162</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>44165</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44166</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44168</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44169</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41249,7 +41249,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46627,7 +46627,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46912,7 +46912,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47311,7 +47311,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49673,7 +49673,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49730,7 +49730,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50072,7 +50072,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51802,7 +51802,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52600,7 +52600,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53175,7 +53175,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54771,7 +54771,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54885,7 +54885,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55170,7 +55170,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55284,7 +55284,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55398,7 +55398,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55455,7 +55455,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55626,7 +55626,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55854,7 +55854,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56025,7 +56025,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56139,7 +56139,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56310,7 +56310,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56367,7 +56367,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56424,7 +56424,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56595,7 +56595,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56652,7 +56652,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56709,7 +56709,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56880,7 +56880,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56937,7 +56937,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57393,7 +57393,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57450,7 +57450,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57849,7 +57849,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58077,7 +58077,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58134,7 +58134,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58191,7 +58191,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58419,7 +58419,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58662,7 +58662,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59096,7 +59096,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59158,7 +59158,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59329,7 +59329,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59500,7 +59500,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59728,7 +59728,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59785,7 +59785,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59842,7 +59842,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59899,7 +59899,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59956,7 +59956,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60241,7 +60241,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60417,7 +60417,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60467,14 +60467,14 @@
     <row r="1008" ht="15" customHeight="1">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>A 4074-2024</t>
+          <t>A 4097-2024</t>
         </is>
       </c>
       <c r="B1008" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         </is>
       </c>
       <c r="G1008" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H1008" t="n">
         <v>0</v>
@@ -60524,14 +60524,14 @@
     <row r="1009" ht="15" customHeight="1">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>A 4097-2024</t>
+          <t>A 4074-2024</t>
         </is>
       </c>
       <c r="B1009" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60544,7 +60544,7 @@
         </is>
       </c>
       <c r="G1009" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -60588,7 +60588,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60645,7 +60645,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60702,7 +60702,7 @@
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60809,14 +60809,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 5056-2024</t>
+          <t>A 5046-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60829,7 +60829,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -60866,14 +60866,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 5054-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60886,7 +60886,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -60923,14 +60923,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 5046-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -60980,14 +60980,14 @@
     <row r="1017" ht="15" customHeight="1">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>A 5054-2024</t>
+          <t>A 5056-2024</t>
         </is>
       </c>
       <c r="B1017" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61000,7 +61000,7 @@
         </is>
       </c>
       <c r="G1017" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="H1017" t="n">
         <v>0</v>
@@ -61037,14 +61037,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 5145-2024</t>
+          <t>A 5111-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61057,7 +61057,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -61094,14 +61094,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 5111-2024</t>
+          <t>A 5145-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -61151,14 +61151,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 5553-2024</t>
+          <t>A 5563-2024</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -61208,14 +61208,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 5616-2024</t>
+          <t>A 5553-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61228,7 +61228,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -61265,14 +61265,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 5563-2024</t>
+          <t>A 5616-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61285,7 +61285,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -61322,14 +61322,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 6117-2024</t>
+          <t>A 6136-2024</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -61379,14 +61379,14 @@
     <row r="1024" ht="15" customHeight="1">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>A 6136-2024</t>
+          <t>A 6123-2024</t>
         </is>
       </c>
       <c r="B1024" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -61436,14 +61436,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 6123-2024</t>
+          <t>A 6117-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -61500,7 +61500,7 @@
         <v>45341</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61557,7 +61557,7 @@
         <v>45341</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61614,7 +61614,7 @@
         <v>45344</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61671,7 +61671,7 @@
         <v>45344</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61718,7 +61718,7 @@
       </c>
       <c r="R1029" s="2" t="inlineStr"/>
     </row>
-    <row r="1030">
+    <row r="1030" ht="15" customHeight="1">
       <c r="A1030" t="inlineStr">
         <is>
           <t>A 7250-2024</t>
@@ -61728,7 +61728,7 @@
         <v>45344</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61774,6 +61774,316 @@
         <v>0</v>
       </c>
       <c r="R1030" s="2" t="inlineStr"/>
+    </row>
+    <row r="1031" ht="15" customHeight="1">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>A 7671-2024</t>
+        </is>
+      </c>
+      <c r="B1031" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C1031" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G1031" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1031" s="2" t="inlineStr"/>
+    </row>
+    <row r="1032" ht="15" customHeight="1">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>A 7675-2024</t>
+        </is>
+      </c>
+      <c r="B1032" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C1032" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G1032" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1032" s="2" t="inlineStr"/>
+    </row>
+    <row r="1033" ht="15" customHeight="1">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>A 7672-2024</t>
+        </is>
+      </c>
+      <c r="B1033" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C1033" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G1033" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1033" s="2" t="inlineStr"/>
+    </row>
+    <row r="1034" ht="15" customHeight="1">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>A 7673-2024</t>
+        </is>
+      </c>
+      <c r="B1034" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C1034" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G1034" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1034" s="2" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>A 7674-2024</t>
+        </is>
+      </c>
+      <c r="B1035" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="C1035" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G1035" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1035" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1035"/>
+  <dimension ref="A1:Z1036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44181</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44267</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44342</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44343</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44356</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44378</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44406</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44411</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44427</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44463</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44494</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44616</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>44778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44786</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44820</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44858</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44978</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45098</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45182</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45195</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45224</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>45225</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>43335</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>43340</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>43357</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>43377</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>43402</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43403</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43404</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>43413</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>43420</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>43421</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>43422</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>43427</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>43430</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>43432</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>43447</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>43452</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>43455</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>43465</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>43469</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>43471</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>43472</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>43473</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>43474</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>43475</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>43476</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>43478</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>43479</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>43482</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>43485</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>43486</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>43488</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>43493</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>43500</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>43507</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>43509</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>43514</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>43516</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>43517</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43529</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43531</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43536</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43538</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43542</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43543</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>43544</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>43549</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43552</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>43558</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>43566</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>43567</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>43579</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>43595</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>43607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43608</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>43613</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43630</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43633</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43640</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43641</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43644</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43648</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43649</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43654</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43655</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43657</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43665</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>43669</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>43675</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>43676</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>43693</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>43696</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>43698</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>43699</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>43703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>43706</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>43707</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43709</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>43713</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>43719</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>43721</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>43726</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>43732</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>43734</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>43737</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>43742</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>43745</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>43749</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>43758</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>43759</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>43767</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>43769</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>43774</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>43775</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>43780</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>43783</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>43787</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>43797</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>43801</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>43805</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>43809</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>43810</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>43815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>43840</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>43843</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>43846</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>43851</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>43853</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>43858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>43859</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>43860</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>43861</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>43864</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>43873</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>43875</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>43878</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>43880</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>43881</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>43882</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>43886</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>43899</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>43901</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>43907</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>43920</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>43921</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>43927</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>43930</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>43937</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>43938</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>43945</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>43951</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>43955</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>43962</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>43965</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>43970</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>43971</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>43976</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>43979</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>43993</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44002</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44011</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44012</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44014</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44028</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44053</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>44069</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>44071</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>44081</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44083</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44098</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44099</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44102</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44103</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44104</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44106</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44118</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44127</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44130</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44133</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44139</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44144</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44145</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44153</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44154</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>44158</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44160</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44162</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>44165</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44166</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44168</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44169</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41249,7 +41249,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45057</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45829,7 +45829,7 @@
         <v>45058</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45063</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45063</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>45063</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45063</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45063</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45063</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45063</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45070</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45070</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45075</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45075</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45075</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45075</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46627,7 +46627,7 @@
         <v>45090</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>45090</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>45090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>45090</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45091</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46912,7 +46912,7 @@
         <v>45091</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>45091</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45092</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>45092</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45096</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45096</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45097</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47311,7 +47311,7 @@
         <v>45097</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>45098</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45098</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
         <v>45098</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45098</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45098</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45099</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45103</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45103</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45103</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45103</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45103</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45103</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45103</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45104</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>45104</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>45104</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45105</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>45105</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>45105</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45105</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45105</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45105</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45106</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45106</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45110</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45110</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>45110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45110</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45110</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45110</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45110</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>45110</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45112</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>45112</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45113</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45113</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45113</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45113</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49673,7 +49673,7 @@
         <v>45113</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49730,7 +49730,7 @@
         <v>45113</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45113</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>45113</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49901,7 +49901,7 @@
         <v>45113</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>45113</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>45113</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50072,7 +50072,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50186,7 +50186,7 @@
         <v>45135</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50243,7 +50243,7 @@
         <v>45135</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45147</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
         <v>45147</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>45148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45154</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45159</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45163</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>45164</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45168</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45168</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45169</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45174</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45174</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>45174</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>45174</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45174</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51279,7 +51279,7 @@
         <v>45174</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>45175</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45175</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>45175</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45176</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51802,7 +51802,7 @@
         <v>45176</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>45180</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51916,7 +51916,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>45182</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>45188</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45188</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45191</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52543,7 +52543,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52600,7 +52600,7 @@
         <v>45196</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>45196</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45198</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>45198</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>45198</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52947,7 +52947,7 @@
         <v>45198</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53004,7 +53004,7 @@
         <v>45202</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>45204</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>45204</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53175,7 +53175,7 @@
         <v>45204</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53232,7 +53232,7 @@
         <v>45204</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53289,7 +53289,7 @@
         <v>45204</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45204</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53403,7 +53403,7 @@
         <v>45204</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53460,7 +53460,7 @@
         <v>45207</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>45207</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>45207</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45208</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>45208</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53745,7 +53745,7 @@
         <v>45209</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45209</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>45209</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45212</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45212</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45212</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
         <v>45212</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>45212</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>45212</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45215</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>45216</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45217</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>45218</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>45218</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>45223</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54714,7 +54714,7 @@
         <v>45223</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54771,7 +54771,7 @@
         <v>45224</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>45224</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54885,7 +54885,7 @@
         <v>45224</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>45224</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>45224</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55056,7 +55056,7 @@
         <v>45225</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>45230</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55170,7 +55170,7 @@
         <v>45231</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55227,7 +55227,7 @@
         <v>45231</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55284,7 +55284,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55341,7 +55341,7 @@
         <v>45237</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55398,7 +55398,7 @@
         <v>45237</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55455,7 +55455,7 @@
         <v>45237</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45237</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55626,7 +55626,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55740,7 +55740,7 @@
         <v>45239</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>45239</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55854,7 +55854,7 @@
         <v>45240</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45240</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>45240</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56025,7 +56025,7 @@
         <v>45240</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45240</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56139,7 +56139,7 @@
         <v>45240</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45240</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>45240</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56310,7 +56310,7 @@
         <v>45240</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56367,7 +56367,7 @@
         <v>45240</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56424,7 +56424,7 @@
         <v>45240</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45240</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>45240</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56595,7 +56595,7 @@
         <v>45240</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56652,7 +56652,7 @@
         <v>45244</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56709,7 +56709,7 @@
         <v>45244</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>45244</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>45244</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56880,7 +56880,7 @@
         <v>45244</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56937,7 +56937,7 @@
         <v>45245</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45245</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>45251</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45251</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>45252</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45252</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>45252</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>45252</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57393,7 +57393,7 @@
         <v>45253</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57450,7 +57450,7 @@
         <v>45253</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45253</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45254</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>45254</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>45254</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45254</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>45256</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57849,7 +57849,7 @@
         <v>45256</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>45256</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>45257</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>45257</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58077,7 +58077,7 @@
         <v>45258</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58134,7 +58134,7 @@
         <v>45258</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58191,7 +58191,7 @@
         <v>45258</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45258</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>45258</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45258</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58419,7 +58419,7 @@
         <v>45260</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>45267</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45267</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58600,7 +58600,7 @@
         <v>45267</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58662,7 +58662,7 @@
         <v>45267</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58724,7 +58724,7 @@
         <v>45267</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>45267</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45267</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45267</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45267</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>45268</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59096,7 +59096,7 @@
         <v>45268</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59158,7 +59158,7 @@
         <v>45272</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45274</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>45279</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59329,7 +59329,7 @@
         <v>45280</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>45280</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>45280</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59500,7 +59500,7 @@
         <v>45280</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59557,7 +59557,7 @@
         <v>45280</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>45280</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>45282</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59728,7 +59728,7 @@
         <v>45287</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59785,7 +59785,7 @@
         <v>45294</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59842,7 +59842,7 @@
         <v>45303</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59899,7 +59899,7 @@
         <v>45303</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59956,7 +59956,7 @@
         <v>45307</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>45308</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45313</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>45314</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>45314</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60241,7 +60241,7 @@
         <v>45315</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>45317</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>45317</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60417,7 +60417,7 @@
         <v>45320</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60474,7 +60474,7 @@
         <v>45323</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60531,7 +60531,7 @@
         <v>45323</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60588,7 +60588,7 @@
         <v>45327</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60645,7 +60645,7 @@
         <v>45328</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60695,14 +60695,14 @@
     <row r="1012" ht="15" customHeight="1">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>A 4880-2024</t>
+          <t>A 5046-2024</t>
         </is>
       </c>
       <c r="B1012" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60715,7 +60715,7 @@
         </is>
       </c>
       <c r="G1012" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H1012" t="n">
         <v>0</v>
@@ -60752,14 +60752,14 @@
     <row r="1013" ht="15" customHeight="1">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>A 4962-2024</t>
+          <t>A 5054-2024</t>
         </is>
       </c>
       <c r="B1013" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60772,7 +60772,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H1013" t="n">
         <v>0</v>
@@ -60809,14 +60809,14 @@
     <row r="1014" ht="15" customHeight="1">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>A 5046-2024</t>
+          <t>A 5055-2024</t>
         </is>
       </c>
       <c r="B1014" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60829,7 +60829,7 @@
         </is>
       </c>
       <c r="G1014" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
       <c r="H1014" t="n">
         <v>0</v>
@@ -60866,14 +60866,14 @@
     <row r="1015" ht="15" customHeight="1">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>A 5054-2024</t>
+          <t>A 4880-2024</t>
         </is>
       </c>
       <c r="B1015" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60886,7 +60886,7 @@
         </is>
       </c>
       <c r="G1015" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -60923,14 +60923,14 @@
     <row r="1016" ht="15" customHeight="1">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>A 5055-2024</t>
+          <t>A 4962-2024</t>
         </is>
       </c>
       <c r="B1016" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         </is>
       </c>
       <c r="G1016" t="n">
-        <v>7.1</v>
+        <v>3.8</v>
       </c>
       <c r="H1016" t="n">
         <v>0</v>
@@ -60987,7 +60987,7 @@
         <v>45329</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61037,14 +61037,14 @@
     <row r="1018" ht="15" customHeight="1">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>A 5111-2024</t>
+          <t>A 5145-2024</t>
         </is>
       </c>
       <c r="B1018" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61057,7 +61057,7 @@
         </is>
       </c>
       <c r="G1018" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="H1018" t="n">
         <v>0</v>
@@ -61094,14 +61094,14 @@
     <row r="1019" ht="15" customHeight="1">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>A 5145-2024</t>
+          <t>A 5111-2024</t>
         </is>
       </c>
       <c r="B1019" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         </is>
       </c>
       <c r="G1019" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="H1019" t="n">
         <v>0</v>
@@ -61151,14 +61151,14 @@
     <row r="1020" ht="15" customHeight="1">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>A 5563-2024</t>
+          <t>A 5553-2024</t>
         </is>
       </c>
       <c r="B1020" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="H1020" t="n">
         <v>0</v>
@@ -61208,14 +61208,14 @@
     <row r="1021" ht="15" customHeight="1">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>A 5553-2024</t>
+          <t>A 5616-2024</t>
         </is>
       </c>
       <c r="B1021" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61228,7 +61228,7 @@
         </is>
       </c>
       <c r="G1021" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -61265,14 +61265,14 @@
     <row r="1022" ht="15" customHeight="1">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>A 5616-2024</t>
+          <t>A 5563-2024</t>
         </is>
       </c>
       <c r="B1022" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61285,7 +61285,7 @@
         </is>
       </c>
       <c r="G1022" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="H1022" t="n">
         <v>0</v>
@@ -61322,14 +61322,14 @@
     <row r="1023" ht="15" customHeight="1">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>A 6136-2024</t>
+          <t>A 6117-2024</t>
         </is>
       </c>
       <c r="B1023" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         </is>
       </c>
       <c r="G1023" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H1023" t="n">
         <v>0</v>
@@ -61379,14 +61379,14 @@
     <row r="1024" ht="15" customHeight="1">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>A 6123-2024</t>
+          <t>A 6136-2024</t>
         </is>
       </c>
       <c r="B1024" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         </is>
       </c>
       <c r="G1024" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1024" t="n">
         <v>0</v>
@@ -61436,14 +61436,14 @@
     <row r="1025" ht="15" customHeight="1">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>A 6117-2024</t>
+          <t>A 6123-2024</t>
         </is>
       </c>
       <c r="B1025" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         </is>
       </c>
       <c r="G1025" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="H1025" t="n">
         <v>0</v>
@@ -61500,7 +61500,7 @@
         <v>45341</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61557,7 +61557,7 @@
         <v>45341</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61614,7 +61614,7 @@
         <v>45344</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61671,7 +61671,7 @@
         <v>45344</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61728,7 +61728,7 @@
         <v>45344</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61785,7 +61785,7 @@
         <v>45348</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>45348</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61909,7 +61909,7 @@
         <v>45348</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61964,14 +61964,14 @@
     <row r="1034" ht="15" customHeight="1">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>A 7673-2024</t>
+          <t>A 7674-2024</t>
         </is>
       </c>
       <c r="B1034" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61989,7 +61989,7 @@
         </is>
       </c>
       <c r="G1034" t="n">
-        <v>15.8</v>
+        <v>2</v>
       </c>
       <c r="H1034" t="n">
         <v>0</v>
@@ -62023,67 +62023,124 @@
       </c>
       <c r="R1034" s="2" t="inlineStr"/>
     </row>
-    <row r="1035">
+    <row r="1035" ht="15" customHeight="1">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>A 7674-2024</t>
+          <t>A 7673-2024</t>
         </is>
       </c>
       <c r="B1035" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1035" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="G1035" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1035" s="2" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>A 7813-2024</t>
+        </is>
+      </c>
+      <c r="B1036" s="1" t="n">
         <v>45349</v>
       </c>
-      <c r="D1035" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="E1035" t="inlineStr">
-        <is>
-          <t>OSKARSHAMN</t>
-        </is>
-      </c>
-      <c r="F1035" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="G1035" t="n">
-        <v>2</v>
-      </c>
-      <c r="H1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="K1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="P1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="R1035" s="2" t="inlineStr"/>
+      <c r="C1036" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>OSKARSHAMN</t>
+        </is>
+      </c>
+      <c r="G1036" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1036" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt OSKARSHAMN.xlsx
+++ b/Översikt OSKARSHAMN.xlsx
@@ -569,7 +569,7 @@
         <v>44984</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>43710</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>43863</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>44413</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44153</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>44165</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>43742</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>44952</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>43509</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>43509</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44302</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>44356</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>44356</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45244</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45175</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>43517</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>44356</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>44356</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44574</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45170</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>43883</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>45012</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>45230</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>43545</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44161</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>44340</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44515</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44552</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>44568</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44978</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45113</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45218</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45223</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>43420</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>43657</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>43671</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>43671</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44062</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44076</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44181</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>44267</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>44342</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44343</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44356</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44356</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44378</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44406</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>44411</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>44427</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44463</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44494</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44616</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>44778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44786</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44820</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44858</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44978</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45098</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45182</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45195</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>45224</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>45225</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>43335</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>43335</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>43335</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>43339</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>43340</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>43357</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>43369</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>43369</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>43377</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>43402</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>43403</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>43403</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>43404</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>43404</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>43413</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>43420</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>43420</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>43420</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>43420</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>43421</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>43421</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>43422</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>43424</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>43424</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>43424</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>43427</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>43430</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>43432</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>43440</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>43447</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>43447</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>43447</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>43447</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>43452</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>43452</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>43453</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>43454</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>43455</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>43465</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>43465</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>43469</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>43471</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>43472</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>43473</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>43474</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>43475</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>43476</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>43478</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>43479</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>43482</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>43485</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>43486</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>43486</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>43486</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>43488</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>43493</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>43493</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>43500</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>43500</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>43500</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>43507</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>43509</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>43514</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>43516</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>43517</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>43529</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>43531</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>43536</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>43538</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>43542</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>43542</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43543</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>43544</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>43549</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>43552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>43552</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>43556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>43557</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>43557</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>43558</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>43566</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>43567</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>43579</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>43587</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>43595</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>43595</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>43595</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>43595</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>43606</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>43607</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>43608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>43608</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>43608</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>43613</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>43619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>43619</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>43619</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43630</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>43633</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>43640</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>43640</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>43640</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>43641</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>43644</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>43644</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>43647</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>43648</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>43648</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>43649</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>43649</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43654</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>43654</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>43655</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>43657</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>43657</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>43657</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>43657</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>43665</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>43665</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>43665</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>43669</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>43675</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>43675</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>43675</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>43675</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>43675</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>43676</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>43693</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>43696</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>43698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>43698</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>43698</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>43698</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>43699</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>43703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>43706</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>43707</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>43709</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>43713</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>43718</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>43719</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>43721</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>43726</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>43726</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>43732</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>43734</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>43737</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>43742</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>43745</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>43749</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>43749</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>43749</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>43758</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>43759</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>43759</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>43761</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>43767</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>43769</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>43774</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>43774</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>43775</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>43775</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>43780</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>43780</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>43780</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>43783</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>43783</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>43787</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>43787</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>43787</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>43797</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>43797</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>43801</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>43805</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>43809</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>43809</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>43809</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>43809</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>43809</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>43809</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>43809</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>43810</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>43810</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>43815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>43818</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>43818</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>43835</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>43837</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>43840</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>43843</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>43843</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>43846</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>43851</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>43851</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>43851</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>43851</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>43853</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>43858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>43859</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>43859</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>43860</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>43860</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>43861</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>43861</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>43864</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>43864</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>43873</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>43875</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>43875</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>43875</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>43875</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>43878</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>43880</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>43881</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>43882</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>43882</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>43882</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>43882</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>43883</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>43886</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>43899</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>43899</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>43901</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>43901</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>43907</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>43920</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>43921</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>43927</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>43930</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>43937</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>43938</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>43945</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>43951</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>43955</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>43955</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>43962</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>43965</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>43970</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>43971</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>43976</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>43976</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>43976</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>43976</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>43979</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>43993</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>43993</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44002</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>44007</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44011</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44012</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44014</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>44014</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>44014</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44028</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>44053</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44069</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>44069</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>44071</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>44081</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>44081</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>44083</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44083</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44098</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44098</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>44099</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44099</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44102</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>44102</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>44103</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>44103</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44104</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>44106</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>44106</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44118</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44127</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44127</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44127</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44130</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>44133</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44139</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>44144</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>44145</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>44153</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44153</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44153</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44153</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44154</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44154</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>44158</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44160</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44162</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>44165</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>44166</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>44168</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>44168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>44168</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>44169</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44181</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>44181</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44183</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44186</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44186</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44208</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44211</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>44222</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>44222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>44222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>44228</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44232</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>44245</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44245</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44245</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>44245</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44251</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>44251</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44252</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44253</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>44261</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>44262</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44263</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44271</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>44272</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>44272</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44272</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>44298</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>44302</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44307</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44308</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>44313</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44315</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44315</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>44320</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44335</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44342</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44342</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44348</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44348</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44348</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44348</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44350</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>44355</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>44356</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44365</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44377</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44378</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44389</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>44395</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>44399</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>44399</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44403</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44406</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44426</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44426</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>44426</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44427</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44428</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44431</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>44434</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>44440</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44443</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44446</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>44446</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>44447</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44452</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>44455</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44455</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>44455</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44455</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27917,7 +27917,7 @@
         <v>44455</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>44455</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44461</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>44467</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>44469</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44470</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44476</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44477</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44477</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44483</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44483</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44488</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44488</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44488</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44489</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44489</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44489</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44490</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44494</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44497</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44501</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44503</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44505</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44515</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44515</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44515</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44515</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44515</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44516</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44517</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44524</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44538</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44539</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44539</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>44539</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>44539</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>44539</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>44539</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44544</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44544</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>44546</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>44546</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>44547</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>44551</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44552</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44552</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>44564</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>44564</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>44573</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>44573</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44575</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44579</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44580</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>44586</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>44587</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>44588</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>44593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>44593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>44593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44593</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>44594</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>44595</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44596</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44596</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>44602</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44603</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44608</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>44613</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44616</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44620</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>44621</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>44621</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44621</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>44621</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44624</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44627</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44629</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>44630</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>44650</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>44656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         <v>44656</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>44662</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>44663</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44664</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44664</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>44677</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44677</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44683</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44683</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44685</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44697</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44704</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44711</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44711</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44711</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>44711</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>44711</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44712</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>44712</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44712</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>44713</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44713</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>44726</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>44733</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>44743</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>44749</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34510,7 +34510,7 @@
         <v>44749</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>44754</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>44755</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34681,7 +34681,7 @@
         <v>44755</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>44755</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>44756</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>44756</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>44756</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>44762</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35023,7 +35023,7 @@
         <v>44761</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>44762</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35137,7 +35137,7 @@
         <v>44762</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>44763</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>44767</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>44767</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>44768</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>44768</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>44774</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>44778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>44781</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>44785</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>44789</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>44789</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44791</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44791</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>44803</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44806</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>44817</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>44818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>44818</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44818</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36411,7 +36411,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>44820</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44820</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44825</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44831</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44833</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44836</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>44837</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37152,7 +37152,7 @@
         <v>44841</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>44851</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>44851</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>44852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>44855</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>44858</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>44860</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44861</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>44862</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>44862</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>44865</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>44865</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>44865</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>44865</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>44865</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>44865</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>44865</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44866</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>44866</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>44868</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44868</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>44869</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>44872</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>44873</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>44874</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>44875</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44879</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44889</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>44889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>44900</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>44908</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>44910</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>44910</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>44914</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39100,7 +39100,7 @@
         <v>44914</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39157,7 +39157,7 @@
         <v>44915</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>44915</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39271,7 +39271,7 @@
         <v>44917</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>44917</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>44917</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>44917</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>44938</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39556,7 +39556,7 @@
         <v>44943</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>44945</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>44945</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>44946</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>44946</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44951</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44951</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>44951</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>44952</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>44952</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>44952</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44956</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44958</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44958</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44960</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44970</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44970</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>44972</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44973</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>44973</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41249,7 +41249,7 @@
         <v>44974</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>44974</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41363,7 +41363,7 @@
         <v>44974</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>44977</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>44978</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>44978</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44978</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>44978</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>44980</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>44980</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>44980</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>44980</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>44980</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>44980</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>44981</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>44984</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>44984</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>44985</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>44986</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>44987</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44987</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44987</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44992</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44992</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>44993</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>44993</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>44993</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>44994</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44994</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44994</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>44994</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43026,7 +43026,7 @@
         <v>44994</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>44995</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>44995</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>44995</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>44995</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>44995</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45002</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45002</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45002</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45002</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45007</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45008</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>45012</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45012</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>45012</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>45012</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43943,7 +43943,7 @@
         <v>45012</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45012</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>45012</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45014</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>45015</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45016</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>45019</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45019</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>45021</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45022</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45022</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45022</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45027</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45027</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>45027</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45028</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45034</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45034</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45034</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45034</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45034</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45036</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45041</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45041</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45043</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>45051</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45051</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>45054</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45544,7 +45544,7 @@
         <v>45056</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45056</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45056</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>45056</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45772,7 +45772,7 @@
         <v>45057</v>
       </c>
       <c